--- a/OrderDetails_Data_Base.xlsx
+++ b/OrderDetails_Data_Base.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\equip\Downloads\Test_NorthWind_Industries\Test_NorthWind_Industries\Sources\Full_Info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B40E5AAE-7336-484B-AFC4-F52CC4DB37BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A4B4058-E902-47FB-A00F-BAFB0BA01543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{92F13726-1377-4D95-A035-830A127EA808}"/>
   </bookViews>
@@ -221,7 +221,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -242,17 +242,6 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -344,26 +333,215 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="13">
+    <dxf>
+      <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ h:mm"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ h:mm"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -386,196 +564,6 @@
         </right>
         <top/>
         <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ h:mm"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ h:mm"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
@@ -594,18 +582,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{083EBA04-9EB5-4853-A02E-3B59925AE8BD}" name="Tabla4" displayName="Tabla4" ref="A1:I73" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="12" tableBorderDxfId="11" totalsRowBorderDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{083EBA04-9EB5-4853-A02E-3B59925AE8BD}" name="Tabla4" displayName="Tabla4" ref="A1:I73" totalsRowShown="0" headerRowDxfId="12" headerRowBorderDxfId="11" tableBorderDxfId="10" totalsRowBorderDxfId="9">
   <autoFilter ref="A1:I73" xr:uid="{083EBA04-9EB5-4853-A02E-3B59925AE8BD}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{D867EA3F-EFE2-4914-ACAA-67346911D395}" name="OrderDetailID" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{53B38CDC-3D99-42B0-B0F8-9FE7D863E087}" name="OrderID" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{C342C51E-594D-442F-ACC1-6CA563B2C270}" name="ProductID" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{932B25C1-DC74-4B19-8927-C362917B0D13}" name="Quantity" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{0BD3206E-1B2E-498E-A2A1-8BCC9672316C}" name="UnitPrice" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{18808030-56F5-4054-953F-54DE0FD29021}" name="AddedBy" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{D681A63B-7705-4803-89DF-048CB21EF33D}" name="AddedOn" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{4F06A193-2E46-4AEB-A915-F347E0877433}" name="ModifiedBy" dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{917F9D2C-7D63-46F8-8811-8C1A91583781}" name="ModifiedOn" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{D867EA3F-EFE2-4914-ACAA-67346911D395}" name="OrderDetailID" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{53B38CDC-3D99-42B0-B0F8-9FE7D863E087}" name="OrderID" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{C342C51E-594D-442F-ACC1-6CA563B2C270}" name="ProductID" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{932B25C1-DC74-4B19-8927-C362917B0D13}" name="Quantity" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{0BD3206E-1B2E-498E-A2A1-8BCC9672316C}" name="UnitPrice" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{18808030-56F5-4054-953F-54DE0FD29021}" name="AddedBy" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{D681A63B-7705-4803-89DF-048CB21EF33D}" name="AddedOn" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{4F06A193-2E46-4AEB-A915-F347E0877433}" name="ModifiedBy" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{917F9D2C-7D63-46F8-8811-8C1A91583781}" name="ModifiedOn" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -928,7 +916,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B72E0EB-B5EF-4F21-8C6D-570CCE55AC53}">
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:K73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
@@ -941,32 +929,32 @@
     <col min="9" max="9" width="15.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="11" t="s">
         <v>3</v>
       </c>
     </row>
@@ -974,7 +962,7 @@
       <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>30</v>
       </c>
       <c r="C2" s="2">
@@ -996,7 +984,7 @@
         <v>4</v>
       </c>
       <c r="I2" s="6">
-        <v>45190.500694444447</v>
+        <v>46224.500694444447</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -1025,7 +1013,7 @@
         <v>4</v>
       </c>
       <c r="I3" s="6">
-        <v>45190.500694444447</v>
+        <v>46225.500694444447</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -1054,14 +1042,14 @@
         <v>4</v>
       </c>
       <c r="I4" s="6">
-        <v>45190.500694444447</v>
+        <v>46226.500694444447</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>13</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>31</v>
       </c>
       <c r="C5" s="2">
@@ -1083,7 +1071,7 @@
         <v>4</v>
       </c>
       <c r="I5" s="6">
-        <v>45194.503472222219</v>
+        <v>46227.500694444447</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -1112,14 +1100,14 @@
         <v>4</v>
       </c>
       <c r="I6" s="6">
-        <v>45194.503472222219</v>
+        <v>46228.500694444447</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>15</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="2">
@@ -1141,7 +1129,7 @@
         <v>4</v>
       </c>
       <c r="I7" s="6">
-        <v>45198.508333333331</v>
+        <v>46229.500694444447</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -1170,7 +1158,7 @@
         <v>4</v>
       </c>
       <c r="I8" s="6">
-        <v>45198.508333333331</v>
+        <v>46230.500694444447</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -1199,7 +1187,7 @@
         <v>4</v>
       </c>
       <c r="I9" s="6">
-        <v>45198.508333333331</v>
+        <v>46231.500694444447</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -1228,14 +1216,14 @@
         <v>4</v>
       </c>
       <c r="I10" s="6">
-        <v>45202.512499999997</v>
+        <v>46232.500694444447</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>21</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="8" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="2">
@@ -1257,7 +1245,7 @@
         <v>4</v>
       </c>
       <c r="I11" s="6">
-        <v>45190.500694444447</v>
+        <v>46233.500694444447</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -1286,7 +1274,7 @@
         <v>4</v>
       </c>
       <c r="I12" s="6">
-        <v>45204.515972222223</v>
+        <v>46234.500694444447</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -1315,14 +1303,14 @@
         <v>4</v>
       </c>
       <c r="I13" s="6">
-        <v>45204.515972222223</v>
+        <v>46235.500694444447</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>27</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="8" t="s">
         <v>33</v>
       </c>
       <c r="C14" s="2">
@@ -1344,7 +1332,7 @@
         <v>4</v>
       </c>
       <c r="I14" s="6">
-        <v>45204.515972222223</v>
+        <v>46236.500694444447</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -1373,14 +1361,14 @@
         <v>4</v>
       </c>
       <c r="I15" s="6">
-        <v>45204.515972222223</v>
+        <v>46237.500694444447</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>37</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="8" t="s">
         <v>34</v>
       </c>
       <c r="C16" s="2">
@@ -1402,14 +1390,14 @@
         <v>4</v>
       </c>
       <c r="I16" s="6">
-        <v>45206.518055555556</v>
+        <v>46238.500694444447</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>38</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="8" t="s">
         <v>34</v>
       </c>
       <c r="C17" s="2">
@@ -1431,14 +1419,14 @@
         <v>4</v>
       </c>
       <c r="I17" s="6">
-        <v>45206.518055555556</v>
+        <v>46239.500694444447</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>39</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="8" t="s">
         <v>34</v>
       </c>
       <c r="C18" s="2">
@@ -1460,7 +1448,7 @@
         <v>4</v>
       </c>
       <c r="I18" s="6">
-        <v>45206.518055555556</v>
+        <v>46240.500694444447</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -1489,7 +1477,7 @@
         <v>4</v>
       </c>
       <c r="I19" s="6">
-        <v>45206.518055555556</v>
+        <v>46241.500694444447</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -1518,14 +1506,14 @@
         <v>4</v>
       </c>
       <c r="I20" s="6">
-        <v>45206.518055555556</v>
+        <v>46242.500694444447</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>42</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="8" t="s">
         <v>35</v>
       </c>
       <c r="C21" s="2">
@@ -1547,7 +1535,7 @@
         <v>4</v>
       </c>
       <c r="I21" s="6">
-        <v>45202.51458333333</v>
+        <v>46243.500694444447</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -1576,14 +1564,14 @@
         <v>4</v>
       </c>
       <c r="I22" s="6">
-        <v>45206.519444444442</v>
+        <v>46244.500694444447</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>45</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="8" t="s">
         <v>36</v>
       </c>
       <c r="C23" s="2">
@@ -1605,7 +1593,7 @@
         <v>4</v>
       </c>
       <c r="I23" s="6">
-        <v>45208.520138888889</v>
+        <v>46245.500694444447</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -1634,7 +1622,7 @@
         <v>4</v>
       </c>
       <c r="I24" s="6">
-        <v>45208.520138888889</v>
+        <v>46246.500694444447</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -1663,7 +1651,7 @@
         <v>4</v>
       </c>
       <c r="I25" s="6">
-        <v>45208.520138888889</v>
+        <v>46247.500694444447</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -1692,7 +1680,7 @@
         <v>4</v>
       </c>
       <c r="I26" s="6">
-        <v>45210.520833333336</v>
+        <v>46248.500694444447</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -1721,14 +1709,14 @@
         <v>4</v>
       </c>
       <c r="I27" s="6">
-        <v>45210.520833333336</v>
+        <v>46249.500694444447</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>50</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="8" t="s">
         <v>37</v>
       </c>
       <c r="C28" s="2">
@@ -1750,7 +1738,7 @@
         <v>4</v>
       </c>
       <c r="I28" s="6">
-        <v>45210.520833333336</v>
+        <v>46250.500694444447</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
@@ -1779,7 +1767,7 @@
         <v>4</v>
       </c>
       <c r="I29" s="6">
-        <v>45210.520833333336</v>
+        <v>46251.500694444447</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -1808,14 +1796,14 @@
         <v>4</v>
       </c>
       <c r="I30" s="6">
-        <v>45210.522916666669</v>
+        <v>46252.500694444447</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>61</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="B31" s="8" t="s">
         <v>38</v>
       </c>
       <c r="C31" s="2">
@@ -1837,7 +1825,7 @@
         <v>4</v>
       </c>
       <c r="I31" s="6">
-        <v>45210.522916666669</v>
+        <v>46253.500694444447</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -1866,7 +1854,7 @@
         <v>4</v>
       </c>
       <c r="I32" s="6">
-        <v>45210.522916666669</v>
+        <v>46254.500694444447</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
@@ -1895,14 +1883,14 @@
         <v>4</v>
       </c>
       <c r="I33" s="6">
-        <v>45210.522916666669</v>
+        <v>46255.500694444447</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>71</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="8" t="s">
         <v>39</v>
       </c>
       <c r="C34" s="2">
@@ -1924,14 +1912,14 @@
         <v>4</v>
       </c>
       <c r="I34" s="6">
-        <v>45212.529166666667</v>
+        <v>46256.500694444447</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>72</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="B35" s="8" t="s">
         <v>39</v>
       </c>
       <c r="C35" s="2">
@@ -1953,7 +1941,7 @@
         <v>4</v>
       </c>
       <c r="I35" s="6">
-        <v>45212.529166666667</v>
+        <v>46257.500694444447</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
@@ -1982,7 +1970,7 @@
         <v>4</v>
       </c>
       <c r="I36" s="6">
-        <v>45212.529166666667</v>
+        <v>46258.500694444447</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
@@ -2011,14 +1999,14 @@
         <v>4</v>
       </c>
       <c r="I37" s="6">
-        <v>45214.529861111114</v>
+        <v>46259.500694444447</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>75</v>
       </c>
-      <c r="B38" s="9" t="s">
+      <c r="B38" s="8" t="s">
         <v>40</v>
       </c>
       <c r="C38" s="2">
@@ -2040,14 +2028,14 @@
         <v>4</v>
       </c>
       <c r="I38" s="6">
-        <v>45214.529861111114</v>
+        <v>46260.500694444447</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>76</v>
       </c>
-      <c r="B39" s="9" t="s">
+      <c r="B39" s="8" t="s">
         <v>40</v>
       </c>
       <c r="C39" s="2">
@@ -2069,14 +2057,14 @@
         <v>4</v>
       </c>
       <c r="I39" s="6">
-        <v>45214.529861111114</v>
+        <v>46261.500694444447</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>79</v>
       </c>
-      <c r="B40" s="9" t="s">
+      <c r="B40" s="8" t="s">
         <v>41</v>
       </c>
       <c r="C40" s="2">
@@ -2098,7 +2086,7 @@
         <v>4</v>
       </c>
       <c r="I40" s="6">
-        <v>45214.531944444447</v>
+        <v>46262.500694444447</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -2127,7 +2115,7 @@
         <v>4</v>
       </c>
       <c r="I41" s="6">
-        <v>45214.531944444447</v>
+        <v>46263.500694444447</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -2156,14 +2144,14 @@
         <v>4</v>
       </c>
       <c r="I42" s="6">
-        <v>45216.533333333333</v>
+        <v>46264.500694444447</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>85</v>
       </c>
-      <c r="B43" s="9" t="s">
+      <c r="B43" s="8" t="s">
         <v>42</v>
       </c>
       <c r="C43" s="2">
@@ -2185,7 +2173,7 @@
         <v>4</v>
       </c>
       <c r="I43" s="6">
-        <v>45216.533333333333</v>
+        <v>46265.500694444447</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
@@ -2214,7 +2202,7 @@
         <v>4</v>
       </c>
       <c r="I44" s="6">
-        <v>45216.533333333333</v>
+        <v>46266.500694444447</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
@@ -2243,14 +2231,14 @@
         <v>4</v>
       </c>
       <c r="I45" s="6">
-        <v>45218.534722222219</v>
+        <v>46267.500694444447</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>93</v>
       </c>
-      <c r="B46" s="9" t="s">
+      <c r="B46" s="8" t="s">
         <v>43</v>
       </c>
       <c r="C46" s="2">
@@ -2272,14 +2260,14 @@
         <v>4</v>
       </c>
       <c r="I46" s="6">
-        <v>45218.534722222219</v>
+        <v>46268.500694444447</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>96</v>
       </c>
-      <c r="B47" s="9" t="s">
+      <c r="B47" s="8" t="s">
         <v>44</v>
       </c>
       <c r="C47" s="2">
@@ -2301,7 +2289,7 @@
         <v>4</v>
       </c>
       <c r="I47" s="6">
-        <v>45218.535416666666</v>
+        <v>46269.500694444447</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
@@ -2330,7 +2318,7 @@
         <v>4</v>
       </c>
       <c r="I48" s="6">
-        <v>45218.535416666666</v>
+        <v>46270.500694444447</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
@@ -2359,14 +2347,14 @@
         <v>4</v>
       </c>
       <c r="I49" s="6">
-        <v>45220.536805555559</v>
+        <v>46271.500694444447</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>102</v>
       </c>
-      <c r="B50" s="9" t="s">
+      <c r="B50" s="8" t="s">
         <v>45</v>
       </c>
       <c r="C50" s="2">
@@ -2388,7 +2376,7 @@
         <v>4</v>
       </c>
       <c r="I50" s="6">
-        <v>45220.536805555559</v>
+        <v>46272.500694444447</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
@@ -2417,7 +2405,7 @@
         <v>4</v>
       </c>
       <c r="I51" s="6">
-        <v>45220.536805555559</v>
+        <v>46273.500694444447</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
@@ -2446,14 +2434,14 @@
         <v>4</v>
       </c>
       <c r="I52" s="6">
-        <v>45222.538194444445</v>
+        <v>46274.500694444447</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>110</v>
       </c>
-      <c r="B53" s="9" t="s">
+      <c r="B53" s="8" t="s">
         <v>46</v>
       </c>
       <c r="C53" s="2">
@@ -2475,14 +2463,14 @@
         <v>4</v>
       </c>
       <c r="I53" s="6">
-        <v>45222.538194444445</v>
+        <v>46275.500694444447</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>113</v>
       </c>
-      <c r="B54" s="9" t="s">
+      <c r="B54" s="8" t="s">
         <v>47</v>
       </c>
       <c r="C54" s="2">
@@ -2504,7 +2492,7 @@
         <v>4</v>
       </c>
       <c r="I54" s="6">
-        <v>45222.538888888892</v>
+        <v>46276.500694444447</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
@@ -2533,7 +2521,7 @@
         <v>4</v>
       </c>
       <c r="I55" s="6">
-        <v>45222.538888888892</v>
+        <v>46277.500694444447</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
@@ -2562,14 +2550,14 @@
         <v>4</v>
       </c>
       <c r="I56" s="6">
-        <v>45224.540277777778</v>
+        <v>46278.500694444447</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>119</v>
       </c>
-      <c r="B57" s="9" t="s">
+      <c r="B57" s="8" t="s">
         <v>48</v>
       </c>
       <c r="C57" s="2">
@@ -2591,7 +2579,7 @@
         <v>4</v>
       </c>
       <c r="I57" s="6">
-        <v>45224.540277777778</v>
+        <v>46279.500694444447</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
@@ -2620,7 +2608,7 @@
         <v>4</v>
       </c>
       <c r="I58" s="6">
-        <v>45224.540277777778</v>
+        <v>46280.500694444447</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
@@ -2649,14 +2637,14 @@
         <v>4</v>
       </c>
       <c r="I59" s="6">
-        <v>45226.541666666664</v>
+        <v>46281.500694444447</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
         <v>127</v>
       </c>
-      <c r="B60" s="9" t="s">
+      <c r="B60" s="8" t="s">
         <v>49</v>
       </c>
       <c r="C60" s="2">
@@ -2678,14 +2666,14 @@
         <v>4</v>
       </c>
       <c r="I60" s="6">
-        <v>45226.541666666664</v>
+        <v>46282.500694444447</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
         <v>129</v>
       </c>
-      <c r="B61" s="9" t="s">
+      <c r="B61" s="8" t="s">
         <v>50</v>
       </c>
       <c r="C61" s="2">
@@ -2707,7 +2695,7 @@
         <v>4</v>
       </c>
       <c r="I61" s="6">
-        <v>45226.542361111111</v>
+        <v>46283.500694444447</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
@@ -2736,7 +2724,7 @@
         <v>4</v>
       </c>
       <c r="I62" s="6">
-        <v>45226.542361111111</v>
+        <v>46284.500694444447</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
@@ -2765,14 +2753,14 @@
         <v>4</v>
       </c>
       <c r="I63" s="6">
-        <v>45228.543749999997</v>
+        <v>46285.500694444447</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <v>135</v>
       </c>
-      <c r="B64" s="9" t="s">
+      <c r="B64" s="8" t="s">
         <v>51</v>
       </c>
       <c r="C64" s="2">
@@ -2794,10 +2782,10 @@
         <v>4</v>
       </c>
       <c r="I64" s="6">
-        <v>45228.543749999997</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+        <v>46286.500694444447</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <v>136</v>
       </c>
@@ -2823,10 +2811,11 @@
         <v>4</v>
       </c>
       <c r="I65" s="6">
-        <v>45228.543749999997</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+        <v>46287.500694444447</v>
+      </c>
+      <c r="K65" s="12"/>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <v>142</v>
       </c>
@@ -2852,14 +2841,14 @@
         <v>4</v>
       </c>
       <c r="I66" s="6">
-        <v>45230.545138888891</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+        <v>46288.500694444447</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <v>143</v>
       </c>
-      <c r="B67" s="9" t="s">
+      <c r="B67" s="8" t="s">
         <v>52</v>
       </c>
       <c r="C67" s="2">
@@ -2881,10 +2870,10 @@
         <v>4</v>
       </c>
       <c r="I67" s="6">
-        <v>45230.545138888891</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+        <v>46289.500694444447</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <v>145</v>
       </c>
@@ -2910,14 +2899,14 @@
         <v>4</v>
       </c>
       <c r="I68" s="6">
-        <v>45230.545138888891</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+        <v>46290.500694444447</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
         <v>146</v>
       </c>
-      <c r="B69" s="9" t="s">
+      <c r="B69" s="8" t="s">
         <v>53</v>
       </c>
       <c r="C69" s="2">
@@ -2939,10 +2928,10 @@
         <v>4</v>
       </c>
       <c r="I69" s="6">
-        <v>45230.54583333333</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+        <v>46291.500694444447</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
         <v>147</v>
       </c>
@@ -2968,10 +2957,10 @@
         <v>4</v>
       </c>
       <c r="I70" s="6">
-        <v>45230.54583333333</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+        <v>46292.500694444447</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
         <v>148</v>
       </c>
@@ -2997,10 +2986,10 @@
         <v>4</v>
       </c>
       <c r="I71" s="6">
-        <v>45232.546527777777</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+        <v>46293.500694444447</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
         <v>149</v>
       </c>
@@ -3026,10 +3015,10 @@
         <v>4</v>
       </c>
       <c r="I72" s="6">
-        <v>45232.546527777777</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+        <v>46294.500694444447</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>150</v>
       </c>
@@ -3054,14 +3043,15 @@
       <c r="H73" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I73" s="8">
-        <v>45234.547222222223</v>
+      <c r="I73" s="6">
+        <v>46295.500694444447</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/OrderDetails_Data_Base.xlsx
+++ b/OrderDetails_Data_Base.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\equip\Downloads\Test_NorthWind_Industries\Test_NorthWind_Industries\Sources\Full_Info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A4B4058-E902-47FB-A00F-BAFB0BA01543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A151CA02-858A-49BE-86B8-EAFE4B25AD9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{92F13726-1377-4D95-A035-830A127EA808}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="55">
   <si>
     <t>AddedBy</t>
   </si>
@@ -198,14 +198,31 @@
   </si>
   <si>
     <t>066</t>
+  </si>
+  <si>
+    <t>$2,100</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -333,7 +350,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -346,7 +363,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -582,8 +600,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{083EBA04-9EB5-4853-A02E-3B59925AE8BD}" name="Tabla4" displayName="Tabla4" ref="A1:I73" totalsRowShown="0" headerRowDxfId="12" headerRowBorderDxfId="11" tableBorderDxfId="10" totalsRowBorderDxfId="9">
-  <autoFilter ref="A1:I73" xr:uid="{083EBA04-9EB5-4853-A02E-3B59925AE8BD}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{083EBA04-9EB5-4853-A02E-3B59925AE8BD}" name="Tabla4" displayName="Tabla4" ref="A1:I74" totalsRowShown="0" headerRowDxfId="12" headerRowBorderDxfId="11" tableBorderDxfId="10" totalsRowBorderDxfId="9">
+  <autoFilter ref="A1:I74" xr:uid="{083EBA04-9EB5-4853-A02E-3B59925AE8BD}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{D867EA3F-EFE2-4914-ACAA-67346911D395}" name="OrderDetailID" dataDxfId="8"/>
     <tableColumn id="2" xr3:uid="{53B38CDC-3D99-42B0-B0F8-9FE7D863E087}" name="OrderID" dataDxfId="7"/>
@@ -916,7 +934,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B72E0EB-B5EF-4F21-8C6D-570CCE55AC53}">
-  <dimension ref="A1:K73"/>
+  <dimension ref="A1:K74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
@@ -2813,7 +2831,6 @@
       <c r="I65" s="6">
         <v>46287.500694444447</v>
       </c>
-      <c r="K65" s="12"/>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
@@ -3046,8 +3063,39 @@
       <c r="I73" s="6">
         <v>46295.500694444447</v>
       </c>
+      <c r="K73" s="13"/>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A74" s="12">
+        <v>151</v>
+      </c>
+      <c r="B74" s="4">
+        <v>3</v>
+      </c>
+      <c r="C74" s="4">
+        <v>28</v>
+      </c>
+      <c r="D74" s="4">
+        <v>12</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G74" s="7">
+        <v>45235.547222222223</v>
+      </c>
+      <c r="H74" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="I74" s="6">
+        <v>46305.500694444447</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
